--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/panel_11/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/panel_11/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
@@ -795,10 +795,10 @@
         <v>16.48512</v>
       </c>
       <c r="D22" t="n">
+        <v>16.24105</v>
+      </c>
+      <c r="E22" t="n">
         <v>16.44747</v>
-      </c>
-      <c r="E22" t="n">
-        <v>16.24105</v>
       </c>
       <c r="F22" t="n">
         <v>42.41969</v>
@@ -842,13 +842,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.63167</v>
+        <v>16.66163</v>
       </c>
       <c r="D24" t="n">
         <v>16.47854</v>
       </c>
       <c r="E24" t="n">
-        <v>16.66163</v>
+        <v>16.63167</v>
       </c>
       <c r="F24" t="n">
         <v>42.05892</v>
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.5974</v>
+        <v>16.79043</v>
       </c>
       <c r="D25" t="n">
         <v>16.29446</v>
       </c>
       <c r="E25" t="n">
-        <v>16.79043</v>
+        <v>16.5974</v>
       </c>
       <c r="F25" t="n">
         <v>42.39071</v>
@@ -892,13 +892,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.4371</v>
+        <v>16.73861</v>
       </c>
       <c r="D26" t="n">
         <v>16.29565</v>
       </c>
       <c r="E26" t="n">
-        <v>16.73861</v>
+        <v>16.4371</v>
       </c>
       <c r="F26" t="n">
         <v>41.43981</v>
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>16.69359</v>
+      </c>
+      <c r="D27" t="n">
+        <v>16.11348</v>
+      </c>
+      <c r="E27" t="n">
         <v>16.66347</v>
-      </c>
-      <c r="D27" t="n">
-        <v>16.69359</v>
-      </c>
-      <c r="E27" t="n">
-        <v>16.11348</v>
       </c>
       <c r="F27" t="n">
         <v>42.13233</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.30447</v>
+        <v>16.67324</v>
       </c>
       <c r="D29" t="n">
         <v>16.27108</v>
       </c>
       <c r="E29" t="n">
-        <v>16.67324</v>
+        <v>16.30447</v>
       </c>
       <c r="F29" t="n">
         <v>41.05355</v>
